--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820329</v>
+        <v>119820324</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487056</v>
+        <v>486774</v>
       </c>
       <c r="R2" t="n">
-        <v>6847048</v>
+        <v>6846910</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820324</v>
+        <v>119820328</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>77866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486774</v>
+        <v>486997</v>
       </c>
       <c r="R3" t="n">
-        <v>6846910</v>
+        <v>6846904</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820328</v>
+        <v>119820325</v>
       </c>
       <c r="B4" t="n">
-        <v>77866</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6443</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486997</v>
+        <v>487365</v>
       </c>
       <c r="R4" t="n">
-        <v>6846904</v>
+        <v>6846682</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820325</v>
+        <v>119820329</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487365</v>
+        <v>487056</v>
       </c>
       <c r="R6" t="n">
-        <v>6846682</v>
+        <v>6847048</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820324</v>
+        <v>119820328</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>77866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486774</v>
+        <v>486997</v>
       </c>
       <c r="R2" t="n">
-        <v>6846910</v>
+        <v>6846904</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820328</v>
+        <v>119820329</v>
       </c>
       <c r="B3" t="n">
-        <v>77866</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486997</v>
+        <v>487056</v>
       </c>
       <c r="R3" t="n">
-        <v>6846904</v>
+        <v>6847048</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820329</v>
+        <v>119820324</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487056</v>
+        <v>486774</v>
       </c>
       <c r="R6" t="n">
-        <v>6847048</v>
+        <v>6846910</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820326</v>
+        <v>119820324</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486972</v>
+        <v>486774</v>
       </c>
       <c r="R5" t="n">
-        <v>6846887</v>
+        <v>6846910</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820324</v>
+        <v>119820326</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486774</v>
+        <v>486972</v>
       </c>
       <c r="R6" t="n">
-        <v>6846910</v>
+        <v>6846887</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820328</v>
+        <v>119820325</v>
       </c>
       <c r="B2" t="n">
-        <v>77866</v>
+        <v>96868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6443</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486997</v>
+        <v>487365</v>
       </c>
       <c r="R2" t="n">
-        <v>6846904</v>
+        <v>6846682</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820329</v>
+        <v>119820326</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487056</v>
+        <v>486972</v>
       </c>
       <c r="R3" t="n">
-        <v>6847048</v>
+        <v>6846887</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820325</v>
+        <v>119820328</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>77866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487365</v>
+        <v>486997</v>
       </c>
       <c r="R4" t="n">
-        <v>6846682</v>
+        <v>6846904</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820324</v>
+        <v>119820329</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486774</v>
+        <v>487056</v>
       </c>
       <c r="R5" t="n">
-        <v>6846910</v>
+        <v>6847048</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820326</v>
+        <v>119820324</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486972</v>
+        <v>486774</v>
       </c>
       <c r="R6" t="n">
-        <v>6846887</v>
+        <v>6846910</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820325</v>
+        <v>119820329</v>
       </c>
       <c r="B2" t="n">
-        <v>96868</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487365</v>
+        <v>487056</v>
       </c>
       <c r="R2" t="n">
-        <v>6846682</v>
+        <v>6847048</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820326</v>
+        <v>119820325</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486972</v>
+        <v>487365</v>
       </c>
       <c r="R3" t="n">
-        <v>6846887</v>
+        <v>6846682</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820328</v>
+        <v>119820326</v>
       </c>
       <c r="B4" t="n">
-        <v>77866</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6443</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486997</v>
+        <v>486972</v>
       </c>
       <c r="R4" t="n">
-        <v>6846904</v>
+        <v>6846887</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820329</v>
+        <v>119820328</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>77882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487056</v>
+        <v>486997</v>
       </c>
       <c r="R5" t="n">
-        <v>6847048</v>
+        <v>6846904</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1122,7 +1122,7 @@
         <v>119820324</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820329</v>
+        <v>119820328</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>77882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487056</v>
+        <v>486997</v>
       </c>
       <c r="R2" t="n">
-        <v>6847048</v>
+        <v>6846904</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820325</v>
+        <v>119820329</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487365</v>
+        <v>487056</v>
       </c>
       <c r="R3" t="n">
-        <v>6846682</v>
+        <v>6847048</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820328</v>
+        <v>119820325</v>
       </c>
       <c r="B5" t="n">
-        <v>77882</v>
+        <v>96891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6443</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486997</v>
+        <v>487365</v>
       </c>
       <c r="R5" t="n">
-        <v>6846904</v>
+        <v>6846682</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 34839-2024 artfynd.xlsx
+++ b/artfynd/A 34839-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820328</v>
+        <v>119820325</v>
       </c>
       <c r="B2" t="n">
-        <v>77882</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6443</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486997</v>
+        <v>487365</v>
       </c>
       <c r="R2" t="n">
-        <v>6846904</v>
+        <v>6846682</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820329</v>
+        <v>119820326</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487056</v>
+        <v>486972</v>
       </c>
       <c r="R3" t="n">
-        <v>6847048</v>
+        <v>6846887</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820326</v>
+        <v>119820328</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>77882</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486972</v>
+        <v>486997</v>
       </c>
       <c r="R4" t="n">
-        <v>6846887</v>
+        <v>6846904</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820325</v>
+        <v>119820329</v>
       </c>
       <c r="B5" t="n">
-        <v>96891</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487365</v>
+        <v>487056</v>
       </c>
       <c r="R5" t="n">
-        <v>6846682</v>
+        <v>6847048</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
